--- a/data/trans_orig/KIDMED_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R2-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2065</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6031</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35444</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32837</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36804</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>46099</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44430</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>42344</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40871</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42763</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>39254</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>44470</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>86,68%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>158</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>88861</t>
+          <t>77788</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85125</t>
+          <t>74853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90624</t>
+          <t>79228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4699</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9967</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5292</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10854</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>152343</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>147075</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>155174</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>158910</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>157242</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>145194</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>143854</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>176667</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>171105</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>179507</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>525</t>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>335577</t>
+          <t>297536</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330103</t>
+          <t>292611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338590</t>
+          <t>300583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8422</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4788</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10723</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>196639</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>191704</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>199185</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>168284</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162349</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171410</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>208976</t>
+          <t>169619</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>163944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>211562</t>
+          <t>172225</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>377261</t>
+          <t>366258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371561</t>
+          <t>360000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381091</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12193</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20847</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10981</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6179</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18218</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>23728</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>15951</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>35203</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>24182</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>16213</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>34777</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>280028</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>271374</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>285384</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>263286</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>256049</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>268088</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>291798</t>
+          <t>243803</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282473</t>
+          <t>236777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>298335</t>
+          <t>248532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,73%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>523830</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>512355</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>531607</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>95,67%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>555084</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>544489</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>563053</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24904</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>664453</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>655166</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>672435</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>636580</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>628230</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>641959</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>600959</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>709203</t>
+          <t>592983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728451</t>
+          <t>606975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1356783</t>
+          <t>1265411</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1343607</t>
+          <t>1252529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1367375</t>
+          <t>1275589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
